--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -916,16 +916,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">36,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF1A2430"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円程度（税抜・本番構成・受講者数により変動）。聖建様名義でのご契約を推奨します</t>
+      <t xml:space="preserve">22,800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円程度（税抜・推奨構成・受講者数により変動）。聖建様名義でのご契約を推奨します</t>
     </r>
   </si>
   <si>
@@ -2811,7 +2811,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">官報・厚生労働省の通達・パブリックコメントを継続監視し、対象</t>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回（月初・月中）、官報・厚生労働省の通達・パブリックコメントを確認。対象</t>
     </r>
     <r>
       <rPr>
@@ -2860,7 +2879,28 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">利用料（本番構成）</t>
+      <t xml:space="preserve">利用料（構成</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・推奨）</t>
     </r>
   </si>
   <si>
@@ -2881,7 +2921,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">冗長構成、</t>
+      <t xml:space="preserve">、</t>
     </r>
     <r>
       <rPr>
@@ -2919,6 +2959,25 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">・自動バックアップ・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PITR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">）、</t>
     </r>
     <r>
@@ -3014,26 +3073,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF1A2430"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AWS Backup</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF1A2430"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。聖建様名義でのご契約を推奨します。受講者数により変動します</t>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAT Gateway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">エンドポイントの活用により不要としています。フル冗長構成（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">36,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円）への変更も可能です</t>
     </r>
   </si>
   <si>
@@ -4286,6 +4383,44 @@
       </rPr>
       <t xml:space="preserve">を有効にします。</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAT Gateway </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">エンドポイントの活用により不要とし、費用を抑えます。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4393,7 +4528,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">聖建様のご負担とします。本番構成で月額</t>
+      <t xml:space="preserve">聖建様のご負担とします。推奨構成（構成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）で月額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22,800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円程度（税抜）を見込みます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EC2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の冗長化と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAT Gateway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を加えたフル冗長構成では</t>
     </r>
     <r>
       <rPr>
@@ -4412,7 +4623,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円程度（税抜）を見込みます。聖建様名義でのご契約を推奨します。</t>
+      <t xml:space="preserve">円程度です。聖建様名義でのご契約を推奨します。</t>
     </r>
   </si>
   <si>
@@ -7262,7 +7473,7 @@
         <v>160</v>
       </c>
       <c r="C9" s="44" t="n">
-        <v>36000</v>
+        <v>22800</v>
       </c>
       <c r="D9" s="72" t="s">
         <v>161</v>
@@ -7318,7 +7529,7 @@
       </c>
       <c r="C16" s="75" t="n">
         <f aca="false">04_月額・別途費用!C7+C9</f>
-        <v>136000</v>
+        <v>122800</v>
       </c>
       <c r="D16" s="33" t="s">
         <v>173</v>
@@ -7769,7 +7980,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="90" t="s">
         <v>218</v>
       </c>
@@ -7791,7 +8002,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="90" t="s">
         <v>223</v>
       </c>

--- a/quote/聖建様_概算見積書・注文書.xlsx
+++ b/quote/聖建様_概算見積書・注文書.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="249">
   <si>
     <t xml:space="preserve">御　見　積　書</t>
   </si>
@@ -257,49 +257,71 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">所在地</t>
-  </si>
-  <si>
-    <t xml:space="preserve">〒　　　　　（ご記入ください）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">営業部　津隈 佑己 様</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEL / FAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（ご記入ください）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登録番号（適格請求書）</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="8.5"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T</t>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〒</t>
     </r>
     <r>
       <rPr>
         <sz val="8.5"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　　　　　　　　　　　</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">担当</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藤原</t>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">464-0075</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　名古屋市千種区内山</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3-18-10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL 052-745-6607</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">登録番号 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T9180001048541</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">担当　藤原</t>
   </si>
   <si>
     <t xml:space="preserve">下記のとおりお見積り申し上げます。</t>
@@ -3538,6 +3560,9 @@
     <t xml:space="preserve">注文番号</t>
   </si>
   <si>
+    <t xml:space="preserve">（ご記入ください）</t>
+  </si>
+  <si>
     <t xml:space="preserve">　　年　　月　　日</t>
   </si>
   <si>
@@ -3547,84 +3572,155 @@
     <t xml:space="preserve">発注者</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">464-0075</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　名古屋市千種区内山</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3-18-10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社聖建</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TEL 052-745-6607</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　／　登録番号 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T9180001048541</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">475-0805</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　愛知県半田市浜田町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丁目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番地</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">担当　藤原 様</t>
   </si>
   <si>
-    <t xml:space="preserve">株式会社聖建</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">475-0805</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　愛知県半田市浜田町</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丁目</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">番地</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">TEL 0569-84-9669</t>
   </si>
   <si>
-    <t xml:space="preserve">ご担当　　　　　　　　　　　　　印</t>
+    <t xml:space="preserve">ご担当　　　　　　　　　　　　　　印</t>
   </si>
   <si>
     <t xml:space="preserve">下記のとおり注文いたします。</t>
@@ -5027,7 +5123,7 @@
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.0\h"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="56">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5105,26 +5201,14 @@
     </font>
     <font>
       <sz val="8.5"/>
-      <color rgb="FF0000FF"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FF6C7A87"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
       <color rgb="FF6C7A87"/>
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9.5"/>
+      <color rgb="FF1A2430"/>
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
@@ -5174,13 +5258,6 @@
       <color rgb="FF1A2430"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FF1A2430"/>
-      <name val="Meiryo"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -5282,6 +5359,12 @@
     <font>
       <sz val="9.5"/>
       <color rgb="FF6C7A87"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF6C7A87"/>
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
@@ -5355,6 +5438,13 @@
     <font>
       <sz val="9.5"/>
       <color rgb="FF1E6B4A"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF1A2430"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -5506,7 +5596,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5539,343 +5629,347 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="55" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="54" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6194,283 +6288,277 @@
       <c r="E9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>14</v>
-      </c>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="C16" s="14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="8" t="s">
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="15" t="n">
         <f aca="false">02_見積明細!F28</f>
         <v>8000000</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18"/>
-      <c r="C18" s="19" t="str">
+      <c r="B18" s="16"/>
+      <c r="C18" s="17" t="str">
         <f aca="false">"消費税 ¥"&amp;TEXT(02_見積明細!F29,"#,##0")&amp;"　／　税込 ¥"&amp;TEXT(02_見積明細!F30,"#,##0")</f>
         <v>消費税 ¥800,000　／　税込 ¥8,800,000</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15" t="s">
+      <c r="C23" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="15" t="s">
+      <c r="C24" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="15" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C27" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15" t="s">
+      <c r="D27" s="21"/>
+      <c r="E27" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="F27" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="21" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="22" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="23" t="s">
+      <c r="C28" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26" t="n">
+      <c r="D28" s="23"/>
+      <c r="E28" s="24" t="n">
         <f aca="false">02_見積明細!D20</f>
         <v>100</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="25" t="n">
         <f aca="false">02_見積明細!F20</f>
         <v>5000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="28" t="n">
+      <c r="B29" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="23"/>
+      <c r="E29" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="F29" s="27" t="n">
+      <c r="F29" s="25" t="n">
         <f aca="false">02_見積明細!F24</f>
         <v>3000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32" t="n">
+      <c r="B30" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30" t="n">
         <f aca="false">02_見積明細!F26</f>
         <v>8000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="35" t="n">
+      <c r="B31" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="33" t="n">
         <f aca="false">02_見積明細!F28</f>
         <v>8000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="35" t="n">
+      <c r="B32" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="33" t="n">
         <f aca="false">02_見積明細!F29</f>
         <v>800000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="38" t="n">
+      <c r="B33" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="36" t="n">
         <f aca="false">02_見積明細!F30</f>
         <v>8800000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="39" t="s">
-        <v>49</v>
+      <c r="B35" s="37" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="B36" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="B37" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="B38" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="24">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
@@ -6514,521 +6602,521 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
+      <c r="F6" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
+    <row r="7" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D4" s="33" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="44" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="23" t="s">
+      <c r="B8" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="C8" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="25" t="n">
         <f aca="false">D8*E8</f>
         <v>400000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="50" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="49" t="n">
+      <c r="A9" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="25" t="n">
         <f aca="false">D9*E9</f>
         <v>350000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="49" t="n">
+      <c r="C10" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="25" t="n">
         <f aca="false">D10*E10</f>
         <v>600000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="49" t="n">
+      <c r="A11" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="47" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="25" t="n">
         <f aca="false">D11*E11</f>
         <v>750000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="49" t="n">
+      <c r="A12" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="25" t="n">
         <f aca="false">D12*E12</f>
         <v>550000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="49" t="n">
+      <c r="A13" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">D13*E13</f>
         <v>150000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="49" t="n">
+      <c r="A14" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="25" t="n">
         <f aca="false">D14*E14</f>
         <v>550000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="49" t="n">
+      <c r="A15" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">D15*E15</f>
         <v>350000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="49" t="n">
+      <c r="A16" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="25" t="n">
         <f aca="false">D16*E16</f>
         <v>350000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="49" t="n">
+      <c r="A17" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="25" t="n">
         <f aca="false">D17*E17</f>
         <v>450000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="49" t="n">
+      <c r="A18" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="25" t="n">
         <f aca="false">D18*E18</f>
         <v>200000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="49" t="n">
+      <c r="A19" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>50000</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="25" t="n">
         <f aca="false">D19*E19</f>
         <v>300000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31"/>
-      <c r="B20" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="53" t="n">
+      <c r="A20" s="29"/>
+      <c r="B20" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="51" t="n">
         <f aca="false">SUM(D8:D19)</f>
         <v>100</v>
       </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32" t="n">
+      <c r="E20" s="29"/>
+      <c r="F20" s="30" t="n">
         <f aca="false">SUM(F8:F19)</f>
         <v>5000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
+      <c r="A22" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
     </row>
     <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="54" t="n">
+      <c r="A23" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="52" t="n">
         <v>10</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="53" t="n">
         <f aca="false">03_教材科目!$C$4</f>
         <v>300000</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="25" t="n">
         <f aca="false">03_教材科目!$F$17</f>
         <v>3000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31"/>
-      <c r="B24" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32" t="n">
+      <c r="A24" s="29"/>
+      <c r="B24" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="30" t="n">
         <f aca="false">F23</f>
         <v>3000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18"/>
-      <c r="B26" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="57" t="n">
+      <c r="A26" s="16"/>
+      <c r="B26" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="55" t="n">
         <f aca="false">D20</f>
         <v>100</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="38" t="n">
+      <c r="E26" s="16"/>
+      <c r="F26" s="36" t="n">
         <f aca="false">F20+F24</f>
         <v>8000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="44" t="n">
+      <c r="B27" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="35" t="n">
+      <c r="B28" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33" t="n">
         <f aca="false">F26+F27</f>
         <v>8000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="59" t="n">
+      <c r="B29" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35" t="n">
+      <c r="E29" s="32"/>
+      <c r="F29" s="33" t="n">
         <f aca="false">ROUND(F28*D29,0)</f>
         <v>800000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="61" t="n">
+      <c r="A30" s="16"/>
+      <c r="B30" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="59" t="n">
         <f aca="false">F28+F29</f>
         <v>8800000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="60" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="61" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="61" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="61" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="61"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="60" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="61" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="63" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="61" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="63" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="61" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="63" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="61" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="63"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="62" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="61" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="63" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="61" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="63" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="61"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="60" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="63" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="61" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="63" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="63" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="63" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="63"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="62" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="63" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -7065,314 +7153,314 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
+      <c r="C6" s="21" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
+      <c r="D6" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D4" s="33" t="s">
+      <c r="E6" s="21" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
+      <c r="F6" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="23" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C7" s="64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D7" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="67" t="n">
+      <c r="E7" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="65" t="n">
+      <c r="A8" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="66" t="n">
+      <c r="B8" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="67" t="n">
+      <c r="D8" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="65" t="n">
+      <c r="A9" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="66" t="n">
+      <c r="B9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="67" t="n">
+      <c r="D9" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="65" t="n">
+      <c r="A10" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="66" t="n">
+      <c r="B10" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="67" t="n">
+      <c r="D10" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="65" t="n">
+      <c r="A11" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="66" t="n">
+      <c r="B11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="64" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="67" t="n">
+      <c r="D11" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="65" t="n">
+      <c r="A12" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="66" t="n">
+      <c r="B12" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="64" t="n">
         <v>4.5</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="67" t="n">
+      <c r="D12" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="n">
+      <c r="A13" s="63" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="66" t="n">
+      <c r="B13" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="64" t="n">
         <v>4.5</v>
       </c>
-      <c r="D13" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="67" t="n">
+      <c r="D13" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="65" t="n">
+      <c r="A14" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="66" t="n">
+      <c r="B14" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="64" t="n">
         <v>5.5</v>
       </c>
-      <c r="D14" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="67" t="n">
+      <c r="D14" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="65" t="n">
+      <c r="A15" s="63" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="66" t="n">
+      <c r="B15" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" s="67" t="n">
+      <c r="D15" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="65" t="n">
+      <c r="A16" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="66" t="n">
+      <c r="B16" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="67" t="n">
+      <c r="D16" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="25" t="n">
         <f aca="false">$C$4</f>
         <v>300000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="68" t="n">
+      <c r="A17" s="16"/>
+      <c r="B17" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="66" t="n">
         <f aca="false">SUM(C7:C16)</f>
         <v>58</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="69" t="n">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="67" t="n">
         <f aca="false">SUM(F7:F16)</f>
         <v>3000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="60" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="61" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="61" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="61" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="61"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="60" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="61" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="61" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="61" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="62" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="63" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -7405,225 +7493,225 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="42" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
+    <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="29"/>
+      <c r="B6" s="56" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="23" t="s">
+      <c r="C6" s="42" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16"/>
+      <c r="B7" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="44" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="44" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18"/>
-      <c r="B7" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="36" t="n">
         <f aca="false">SUM(C5:C6)</f>
         <v>100000</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="42" t="n">
+        <v>22800</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29"/>
+      <c r="B10" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="71" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29"/>
+      <c r="B11" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="44" t="n">
-        <v>22800</v>
-      </c>
-      <c r="D9" s="72" t="s">
+      <c r="C11" s="71" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="31"/>
-      <c r="B10" s="58" t="s">
+      <c r="D11" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="73" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="B13" s="56" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31"/>
-      <c r="B11" s="58" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="70" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="74" t="n">
+      <c r="C13" s="72" t="n">
         <f aca="false">03_教材科目!C4</f>
         <v>300000</v>
       </c>
-      <c r="D13" s="72" t="s">
-        <v>170</v>
+      <c r="D13" s="70" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>171</v>
+      <c r="A15" s="19" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="75" t="n">
+      <c r="B16" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="73" t="n">
         <f aca="false">04_月額・別途費用!C7+C9</f>
         <v>122800</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="60" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="61" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="61" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="61" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="62" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="61"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="60" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="61" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="74" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="61" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="61" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="62" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="74" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="61"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="75" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="76" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="61" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="63" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="61" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="63" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="61" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="76" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="76" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="63"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="77" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="61" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="63" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="63" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="63" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="78" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="63" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -7656,7 +7744,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7665,10 +7753,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7676,238 +7764,252 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="77" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="79"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="8" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="63" t="s">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E10" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="79" t="s">
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="81" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="79"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="11" t="s">
+      <c r="F11" s="81"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="80" t="s">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="F11" s="80"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="20" t="str">
+      <c r="C16" s="18" t="str">
         <f aca="false">01_見積書!C4&amp;"（"&amp;01_見積書!C5&amp;" 発行）"</f>
         <v>SP-2026-0001（2026年9月8日 発行）</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23" t="s">
-        <v>37</v>
+      <c r="A18" s="20"/>
+      <c r="B18" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="21" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="D19" s="26" t="n">
+      <c r="B19" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="82" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="24" t="n">
         <f aca="false">02_見積明細!D20</f>
         <v>100</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="27" t="n">
+      <c r="E19" s="32"/>
+      <c r="F19" s="25" t="n">
         <f aca="false">02_見積明細!F20</f>
         <v>5000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="D20" s="28" t="n">
+      <c r="B20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="27" t="n">
+      <c r="E20" s="32"/>
+      <c r="F20" s="25" t="n">
         <f aca="false">02_見積明細!F24</f>
         <v>3000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32" t="n">
+      <c r="B21" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="30" t="n">
         <f aca="false">SUM(F19:F20)</f>
         <v>8000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="82" t="s">
-        <v>205</v>
-      </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="27" t="n">
+      <c r="B22" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="25" t="n">
         <f aca="false">02_見積明細!F27</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="84" t="n">
+      <c r="B23" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="84"/>
+      <c r="D23" s="85" t="n">
         <f aca="false">02_見積明細!D29</f>
         <v>0.1</v>
       </c>
-      <c r="E23" s="82"/>
-      <c r="F23" s="35" t="n">
+      <c r="E23" s="83"/>
+      <c r="F23" s="33" t="n">
         <f aca="false">ROUND((F21+F22)*D23,0)</f>
         <v>800000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="85" t="n">
+      <c r="B24" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="86" t="n">
         <f aca="false">F21+F22+F23</f>
         <v>8800000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="C30" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="C15:F15"/>
@@ -7942,188 +8044,188 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="87" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="88"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="89" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="86" t="s">
+      <c r="C4" s="90" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="87"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="88" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="89" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="89"/>
+      <c r="C6" s="90" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="88"/>
-      <c r="C5" s="89" t="s">
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="90" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="88"/>
-      <c r="C6" s="89" t="s">
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="91" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="88" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="89" t="s">
+      <c r="C8" s="90" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="90" t="s">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C10" s="88"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="89" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="91" t="s">
+      <c r="C11" s="90" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="87"/>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="88" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C12" s="90" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="90" t="s">
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="89" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C13" s="90" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="88" t="s">
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="89" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C14" s="90" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="88" t="s">
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C15" s="90" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="88" t="s">
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="89" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C16" s="90" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="88" t="s">
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="89" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C17" s="90" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="88" t="s">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="C17" s="89" t="s">
+      <c r="C19" s="88"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="89" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="86" t="s">
+      <c r="C20" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="C19" s="87"/>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="88" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="C20" s="89" t="s">
+      <c r="C21" s="90" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="88" t="s">
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="89" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="89" t="s">
+      <c r="C22" s="90" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="88" t="s">
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="89" t="s">
         <v>240</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C23" s="90" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="88" t="s">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="87" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="89" t="s">
+      <c r="C25" s="88"/>
+    </row>
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="93" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="86" t="s">
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C25" s="87"/>
-    </row>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="88" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="92" t="s">
+      <c r="C27" s="93" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="88" t="s">
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="89" t="s">
         <v>246</v>
       </c>
-      <c r="C27" s="92" t="s">
+      <c r="C28" s="90" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="88" t="s">
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="90" t="s">
         <v>248</v>
-      </c>
-      <c r="C28" s="89" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="89" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
